--- a/data/releases/v4.0/china_city_entity_master_V4.0.xlsx
+++ b/data/releases/v4.0/china_city_entity_master_V4.0.xlsx
@@ -2769,7 +2769,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>1987-2000 呼伦贝尔盟; 2001-2026 呼伦贝尔市</t>
+          <t>1987-2001 呼伦贝尔盟; 2002-2026 呼伦贝尔市</t>
         </is>
       </c>
       <c r="O32" t="n">
@@ -24196,7 +24196,7 @@
         </is>
       </c>
       <c r="H326" t="n">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="I326" t="n">
         <v>2026</v>
@@ -24223,7 +24223,7 @@
       </c>
       <c r="N326" t="inlineStr">
         <is>
-          <t>1987-2002 [not_established]; 2003-2026 中卫市</t>
+          <t>1987-2003 [not_established]; 2004-2026 中卫市</t>
         </is>
       </c>
       <c r="O326" t="n">
